--- a/tester/autofix_qa_tracker.xlsx
+++ b/tester/autofix_qa_tracker.xlsx
@@ -11289,21 +11289,63 @@
         <f>IF(B155="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="B155" s="48" t="n"/>
-      <c r="C155" s="48" t="n"/>
-      <c r="D155" s="48" t="n"/>
+      <c r="B155" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:26</t>
+        </is>
+      </c>
+      <c r="C155" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D155" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="E155" s="48" t="n"/>
       <c r="F155" s="48" t="n"/>
       <c r="G155" s="48" t="n"/>
-      <c r="H155" s="48" t="n"/>
-      <c r="I155" s="48" t="n"/>
-      <c r="J155" s="48" t="n"/>
-      <c r="K155" s="48" t="n"/>
-      <c r="L155" s="48" t="n"/>
-      <c r="M155" s="48" t="n"/>
-      <c r="N155" s="48" t="n"/>
-      <c r="O155" s="48" t="n"/>
-      <c r="R155" s="48" t="n"/>
+      <c r="H155" s="48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I155" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J155" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K155" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="L155" s="48" t="inlineStr">
+        <is>
+          <t>Yok</t>
+        </is>
+      </c>
+      <c r="M155" s="48" t="inlineStr"/>
+      <c r="N155" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O155" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R155" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S155" s="48">
         <f>IF(OR(K155="Evet",N155="Evet",H155="FAIL"),"🚩","")</f>
         <v/>
@@ -11314,21 +11356,67 @@
         <f>IF(B156="","",ROW()-4)</f>
         <v/>
       </c>
-      <c r="B156" s="48" t="n"/>
-      <c r="C156" s="48" t="n"/>
-      <c r="D156" s="48" t="n"/>
+      <c r="B156" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:27</t>
+        </is>
+      </c>
+      <c r="C156" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D156" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
       <c r="E156" s="48" t="n"/>
       <c r="F156" s="48" t="n"/>
       <c r="G156" s="48" t="n"/>
-      <c r="H156" s="48" t="n"/>
-      <c r="I156" s="48" t="n"/>
-      <c r="J156" s="48" t="n"/>
-      <c r="K156" s="48" t="n"/>
-      <c r="L156" s="48" t="n"/>
-      <c r="M156" s="48" t="n"/>
-      <c r="N156" s="48" t="n"/>
-      <c r="O156" s="48" t="n"/>
-      <c r="R156" s="48" t="n"/>
+      <c r="H156" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I156" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J156" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K156" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L156" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="M156" s="48" t="inlineStr">
+        <is>
+          <t>Yanlış ölçüm: beklenen 12.4V, AI '4V' dedi</t>
+        </is>
+      </c>
+      <c r="N156" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O156" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R156" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S156" s="48">
         <f>IF(OR(K156="Evet",N156="Evet",H156="FAIL"),"🚩","")</f>
         <v/>
@@ -11339,9 +11427,63 @@
         <f>IF(B157="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B157" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:27</t>
+        </is>
+      </c>
+      <c r="C157" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D157" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
       <c r="E157" s="48" t="n"/>
       <c r="F157" s="48" t="n"/>
       <c r="G157" s="48" t="n"/>
+      <c r="H157" s="48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I157" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J157" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K157" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="L157" s="48" t="inlineStr">
+        <is>
+          <t>Yok</t>
+        </is>
+      </c>
+      <c r="M157" s="48" t="inlineStr"/>
+      <c r="N157" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O157" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R157" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S157" s="48">
         <f>IF(OR(K157="Evet",N157="Evet",H157="FAIL"),"🚩","")</f>
         <v/>
@@ -11352,9 +11494,63 @@
         <f>IF(B158="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B158" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:27</t>
+        </is>
+      </c>
+      <c r="C158" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D158" s="48" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
       <c r="E158" s="48" t="n"/>
       <c r="F158" s="48" t="n"/>
       <c r="G158" s="48" t="n"/>
+      <c r="H158" s="48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I158" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J158" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K158" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="L158" s="48" t="inlineStr">
+        <is>
+          <t>Yok</t>
+        </is>
+      </c>
+      <c r="M158" s="48" t="inlineStr"/>
+      <c r="N158" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O158" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R158" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S158" s="48">
         <f>IF(OR(K158="Evet",N158="Evet",H158="FAIL"),"🚩","")</f>
         <v/>
@@ -11365,9 +11561,63 @@
         <f>IF(B159="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B159" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:27</t>
+        </is>
+      </c>
+      <c r="C159" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D159" s="48" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
       <c r="E159" s="48" t="n"/>
       <c r="F159" s="48" t="n"/>
       <c r="G159" s="48" t="n"/>
+      <c r="H159" s="48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I159" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J159" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K159" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="L159" s="48" t="inlineStr">
+        <is>
+          <t>Yok</t>
+        </is>
+      </c>
+      <c r="M159" s="48" t="inlineStr"/>
+      <c r="N159" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O159" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R159" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S159" s="48">
         <f>IF(OR(K159="Evet",N159="Evet",H159="FAIL"),"🚩","")</f>
         <v/>
@@ -11378,9 +11628,63 @@
         <f>IF(B160="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B160" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:27</t>
+        </is>
+      </c>
+      <c r="C160" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D160" s="48" t="inlineStr">
+        <is>
+          <t>S06</t>
+        </is>
+      </c>
       <c r="E160" s="48" t="n"/>
       <c r="F160" s="48" t="n"/>
       <c r="G160" s="48" t="n"/>
+      <c r="H160" s="48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I160" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J160" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K160" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="L160" s="48" t="inlineStr">
+        <is>
+          <t>Yok</t>
+        </is>
+      </c>
+      <c r="M160" s="48" t="inlineStr"/>
+      <c r="N160" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O160" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R160" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S160" s="48">
         <f>IF(OR(K160="Evet",N160="Evet",H160="FAIL"),"🚩","")</f>
         <v/>
@@ -11391,9 +11695,63 @@
         <f>IF(B161="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B161" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:27</t>
+        </is>
+      </c>
+      <c r="C161" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D161" s="48" t="inlineStr">
+        <is>
+          <t>S07</t>
+        </is>
+      </c>
       <c r="E161" s="48" t="n"/>
       <c r="F161" s="48" t="n"/>
       <c r="G161" s="48" t="n"/>
+      <c r="H161" s="48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I161" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J161" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K161" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="L161" s="48" t="inlineStr">
+        <is>
+          <t>Yok</t>
+        </is>
+      </c>
+      <c r="M161" s="48" t="inlineStr"/>
+      <c r="N161" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O161" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R161" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S161" s="48">
         <f>IF(OR(K161="Evet",N161="Evet",H161="FAIL"),"🚩","")</f>
         <v/>
@@ -11404,9 +11762,63 @@
         <f>IF(B162="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B162" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:28</t>
+        </is>
+      </c>
+      <c r="C162" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D162" s="48" t="inlineStr">
+        <is>
+          <t>S08</t>
+        </is>
+      </c>
       <c r="E162" s="48" t="n"/>
       <c r="F162" s="48" t="n"/>
       <c r="G162" s="48" t="n"/>
+      <c r="H162" s="48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I162" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J162" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K162" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="L162" s="48" t="inlineStr">
+        <is>
+          <t>Yok</t>
+        </is>
+      </c>
+      <c r="M162" s="48" t="inlineStr"/>
+      <c r="N162" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O162" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R162" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S162" s="48">
         <f>IF(OR(K162="Evet",N162="Evet",H162="FAIL"),"🚩","")</f>
         <v/>
@@ -11417,9 +11829,63 @@
         <f>IF(B163="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B163" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:28</t>
+        </is>
+      </c>
+      <c r="C163" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D163" s="48" t="inlineStr">
+        <is>
+          <t>S09</t>
+        </is>
+      </c>
       <c r="E163" s="48" t="n"/>
       <c r="F163" s="48" t="n"/>
       <c r="G163" s="48" t="n"/>
+      <c r="H163" s="48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I163" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J163" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K163" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="L163" s="48" t="inlineStr">
+        <is>
+          <t>Yok</t>
+        </is>
+      </c>
+      <c r="M163" s="48" t="inlineStr"/>
+      <c r="N163" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O163" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R163" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S163" s="48">
         <f>IF(OR(K163="Evet",N163="Evet",H163="FAIL"),"🚩","")</f>
         <v/>
@@ -11430,9 +11896,63 @@
         <f>IF(B164="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B164" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:28</t>
+        </is>
+      </c>
+      <c r="C164" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D164" s="48" t="inlineStr">
+        <is>
+          <t>S10</t>
+        </is>
+      </c>
       <c r="E164" s="48" t="n"/>
       <c r="F164" s="48" t="n"/>
       <c r="G164" s="48" t="n"/>
+      <c r="H164" s="48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I164" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J164" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K164" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="L164" s="48" t="inlineStr">
+        <is>
+          <t>Yok</t>
+        </is>
+      </c>
+      <c r="M164" s="48" t="inlineStr"/>
+      <c r="N164" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O164" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R164" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S164" s="48">
         <f>IF(OR(K164="Evet",N164="Evet",H164="FAIL"),"🚩","")</f>
         <v/>
@@ -11443,9 +11963,63 @@
         <f>IF(B165="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B165" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:28</t>
+        </is>
+      </c>
+      <c r="C165" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D165" s="48" t="inlineStr">
+        <is>
+          <t>S11</t>
+        </is>
+      </c>
       <c r="E165" s="48" t="n"/>
       <c r="F165" s="48" t="n"/>
       <c r="G165" s="48" t="n"/>
+      <c r="H165" s="48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I165" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J165" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K165" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="L165" s="48" t="inlineStr">
+        <is>
+          <t>Yok</t>
+        </is>
+      </c>
+      <c r="M165" s="48" t="inlineStr"/>
+      <c r="N165" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O165" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R165" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S165" s="48">
         <f>IF(OR(K165="Evet",N165="Evet",H165="FAIL"),"🚩","")</f>
         <v/>
@@ -11456,9 +12030,63 @@
         <f>IF(B166="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B166" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:28</t>
+        </is>
+      </c>
+      <c r="C166" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D166" s="48" t="inlineStr">
+        <is>
+          <t>S12</t>
+        </is>
+      </c>
       <c r="E166" s="48" t="n"/>
       <c r="F166" s="48" t="n"/>
       <c r="G166" s="48" t="n"/>
+      <c r="H166" s="48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I166" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J166" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K166" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="L166" s="48" t="inlineStr">
+        <is>
+          <t>Yok</t>
+        </is>
+      </c>
+      <c r="M166" s="48" t="inlineStr"/>
+      <c r="N166" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O166" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R166" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S166" s="48">
         <f>IF(OR(K166="Evet",N166="Evet",H166="FAIL"),"🚩","")</f>
         <v/>
@@ -11469,9 +12097,63 @@
         <f>IF(B167="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B167" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:28</t>
+        </is>
+      </c>
+      <c r="C167" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D167" s="48" t="inlineStr">
+        <is>
+          <t>S13</t>
+        </is>
+      </c>
       <c r="E167" s="48" t="n"/>
       <c r="F167" s="48" t="n"/>
       <c r="G167" s="48" t="n"/>
+      <c r="H167" s="48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I167" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J167" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K167" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="L167" s="48" t="inlineStr">
+        <is>
+          <t>Yok</t>
+        </is>
+      </c>
+      <c r="M167" s="48" t="inlineStr"/>
+      <c r="N167" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O167" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R167" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S167" s="48">
         <f>IF(OR(K167="Evet",N167="Evet",H167="FAIL"),"🚩","")</f>
         <v/>
@@ -11482,9 +12164,63 @@
         <f>IF(B168="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B168" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:29</t>
+        </is>
+      </c>
+      <c r="C168" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D168" s="48" t="inlineStr">
+        <is>
+          <t>S14</t>
+        </is>
+      </c>
       <c r="E168" s="48" t="n"/>
       <c r="F168" s="48" t="n"/>
       <c r="G168" s="48" t="n"/>
+      <c r="H168" s="48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I168" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J168" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K168" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="L168" s="48" t="inlineStr">
+        <is>
+          <t>Yok</t>
+        </is>
+      </c>
+      <c r="M168" s="48" t="inlineStr"/>
+      <c r="N168" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O168" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R168" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S168" s="48">
         <f>IF(OR(K168="Evet",N168="Evet",H168="FAIL"),"🚩","")</f>
         <v/>
@@ -11495,9 +12231,63 @@
         <f>IF(B169="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B169" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:29</t>
+        </is>
+      </c>
+      <c r="C169" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D169" s="48" t="inlineStr">
+        <is>
+          <t>S15</t>
+        </is>
+      </c>
       <c r="E169" s="48" t="n"/>
       <c r="F169" s="48" t="n"/>
       <c r="G169" s="48" t="n"/>
+      <c r="H169" s="48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I169" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J169" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K169" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="L169" s="48" t="inlineStr">
+        <is>
+          <t>Yok</t>
+        </is>
+      </c>
+      <c r="M169" s="48" t="inlineStr"/>
+      <c r="N169" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O169" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R169" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S169" s="48">
         <f>IF(OR(K169="Evet",N169="Evet",H169="FAIL"),"🚩","")</f>
         <v/>
@@ -11508,9 +12298,63 @@
         <f>IF(B170="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B170" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:38</t>
+        </is>
+      </c>
+      <c r="C170" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D170" s="48" t="inlineStr">
+        <is>
+          <t>S05</t>
+        </is>
+      </c>
       <c r="E170" s="48" t="n"/>
       <c r="F170" s="48" t="n"/>
       <c r="G170" s="48" t="n"/>
+      <c r="H170" s="48" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="I170" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J170" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K170" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="L170" s="48" t="inlineStr">
+        <is>
+          <t>Yok</t>
+        </is>
+      </c>
+      <c r="M170" s="48" t="inlineStr"/>
+      <c r="N170" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O170" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R170" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S170" s="48">
         <f>IF(OR(K170="Evet",N170="Evet",H170="FAIL"),"🚩","")</f>
         <v/>
@@ -11521,9 +12365,67 @@
         <f>IF(B171="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B171" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:41</t>
+        </is>
+      </c>
+      <c r="C171" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D171" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="E171" s="48" t="n"/>
       <c r="F171" s="48" t="n"/>
       <c r="G171" s="48" t="n"/>
+      <c r="H171" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I171" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J171" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K171" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L171" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M171" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N171" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O171" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R171" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S171" s="48">
         <f>IF(OR(K171="Evet",N171="Evet",H171="FAIL"),"🚩","")</f>
         <v/>
@@ -11534,9 +12436,67 @@
         <f>IF(B172="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B172" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:41</t>
+        </is>
+      </c>
+      <c r="C172" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D172" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="E172" s="48" t="n"/>
       <c r="F172" s="48" t="n"/>
       <c r="G172" s="48" t="n"/>
+      <c r="H172" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I172" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J172" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K172" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L172" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M172" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N172" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O172" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R172" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R2</t>
+        </is>
+      </c>
       <c r="S172" s="48">
         <f>IF(OR(K172="Evet",N172="Evet",H172="FAIL"),"🚩","")</f>
         <v/>
@@ -11547,9 +12507,67 @@
         <f>IF(B173="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B173" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:41</t>
+        </is>
+      </c>
+      <c r="C173" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D173" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="E173" s="48" t="n"/>
       <c r="F173" s="48" t="n"/>
       <c r="G173" s="48" t="n"/>
+      <c r="H173" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I173" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J173" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K173" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L173" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M173" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N173" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O173" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R173" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R3</t>
+        </is>
+      </c>
       <c r="S173" s="48">
         <f>IF(OR(K173="Evet",N173="Evet",H173="FAIL"),"🚩","")</f>
         <v/>
@@ -11560,9 +12578,67 @@
         <f>IF(B174="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B174" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:41</t>
+        </is>
+      </c>
+      <c r="C174" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D174" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="E174" s="48" t="n"/>
       <c r="F174" s="48" t="n"/>
       <c r="G174" s="48" t="n"/>
+      <c r="H174" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I174" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J174" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K174" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L174" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M174" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N174" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O174" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R174" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R4</t>
+        </is>
+      </c>
       <c r="S174" s="48">
         <f>IF(OR(K174="Evet",N174="Evet",H174="FAIL"),"🚩","")</f>
         <v/>
@@ -11573,9 +12649,67 @@
         <f>IF(B175="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B175" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:41</t>
+        </is>
+      </c>
+      <c r="C175" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D175" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="E175" s="48" t="n"/>
       <c r="F175" s="48" t="n"/>
       <c r="G175" s="48" t="n"/>
+      <c r="H175" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I175" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J175" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K175" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L175" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M175" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N175" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O175" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R175" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R5</t>
+        </is>
+      </c>
       <c r="S175" s="48">
         <f>IF(OR(K175="Evet",N175="Evet",H175="FAIL"),"🚩","")</f>
         <v/>
@@ -11586,9 +12720,67 @@
         <f>IF(B176="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B176" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:42</t>
+        </is>
+      </c>
+      <c r="C176" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D176" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="E176" s="48" t="n"/>
       <c r="F176" s="48" t="n"/>
       <c r="G176" s="48" t="n"/>
+      <c r="H176" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I176" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J176" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K176" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L176" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M176" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N176" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O176" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R176" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R6</t>
+        </is>
+      </c>
       <c r="S176" s="48">
         <f>IF(OR(K176="Evet",N176="Evet",H176="FAIL"),"🚩","")</f>
         <v/>
@@ -11599,9 +12791,67 @@
         <f>IF(B177="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B177" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:42</t>
+        </is>
+      </c>
+      <c r="C177" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D177" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="E177" s="48" t="n"/>
       <c r="F177" s="48" t="n"/>
       <c r="G177" s="48" t="n"/>
+      <c r="H177" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I177" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J177" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K177" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L177" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M177" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N177" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O177" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R177" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R7</t>
+        </is>
+      </c>
       <c r="S177" s="48">
         <f>IF(OR(K177="Evet",N177="Evet",H177="FAIL"),"🚩","")</f>
         <v/>
@@ -11612,9 +12862,67 @@
         <f>IF(B178="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B178" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:42</t>
+        </is>
+      </c>
+      <c r="C178" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D178" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="E178" s="48" t="n"/>
       <c r="F178" s="48" t="n"/>
       <c r="G178" s="48" t="n"/>
+      <c r="H178" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I178" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J178" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K178" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L178" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M178" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N178" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O178" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R178" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R8</t>
+        </is>
+      </c>
       <c r="S178" s="48">
         <f>IF(OR(K178="Evet",N178="Evet",H178="FAIL"),"🚩","")</f>
         <v/>
@@ -11625,9 +12933,67 @@
         <f>IF(B179="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B179" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:42</t>
+        </is>
+      </c>
+      <c r="C179" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D179" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="E179" s="48" t="n"/>
       <c r="F179" s="48" t="n"/>
       <c r="G179" s="48" t="n"/>
+      <c r="H179" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I179" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J179" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K179" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L179" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M179" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N179" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O179" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R179" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R9</t>
+        </is>
+      </c>
       <c r="S179" s="48">
         <f>IF(OR(K179="Evet",N179="Evet",H179="FAIL"),"🚩","")</f>
         <v/>
@@ -11638,9 +13004,67 @@
         <f>IF(B180="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B180" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:42</t>
+        </is>
+      </c>
+      <c r="C180" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D180" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="E180" s="48" t="n"/>
       <c r="F180" s="48" t="n"/>
       <c r="G180" s="48" t="n"/>
+      <c r="H180" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I180" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J180" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K180" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L180" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M180" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N180" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O180" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R180" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R10</t>
+        </is>
+      </c>
       <c r="S180" s="48">
         <f>IF(OR(K180="Evet",N180="Evet",H180="FAIL"),"🚩","")</f>
         <v/>
@@ -11651,9 +13075,67 @@
         <f>IF(B181="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B181" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:42</t>
+        </is>
+      </c>
+      <c r="C181" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D181" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
       <c r="E181" s="48" t="n"/>
       <c r="F181" s="48" t="n"/>
       <c r="G181" s="48" t="n"/>
+      <c r="H181" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I181" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J181" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K181" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L181" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="M181" s="48" t="inlineStr">
+        <is>
+          <t>Yanlış ölçüm: beklenen 12.4V, AI '4V' dedi</t>
+        </is>
+      </c>
+      <c r="N181" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O181" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R181" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S181" s="48">
         <f>IF(OR(K181="Evet",N181="Evet",H181="FAIL"),"🚩","")</f>
         <v/>
@@ -11664,9 +13146,67 @@
         <f>IF(B182="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B182" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:43</t>
+        </is>
+      </c>
+      <c r="C182" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D182" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
       <c r="E182" s="48" t="n"/>
       <c r="F182" s="48" t="n"/>
       <c r="G182" s="48" t="n"/>
+      <c r="H182" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I182" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J182" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K182" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L182" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M182" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N182" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O182" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R182" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S182" s="48">
         <f>IF(OR(K182="Evet",N182="Evet",H182="FAIL"),"🚩","")</f>
         <v/>
@@ -11677,9 +13217,67 @@
         <f>IF(B183="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B183" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:43</t>
+        </is>
+      </c>
+      <c r="C183" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D183" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
       <c r="E183" s="48" t="n"/>
       <c r="F183" s="48" t="n"/>
       <c r="G183" s="48" t="n"/>
+      <c r="H183" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I183" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J183" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K183" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L183" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="M183" s="48" t="inlineStr">
+        <is>
+          <t>Yanlış ölçüm: beklenen 12.4V, AI '4V' dedi</t>
+        </is>
+      </c>
+      <c r="N183" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O183" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R183" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R2</t>
+        </is>
+      </c>
       <c r="S183" s="48">
         <f>IF(OR(K183="Evet",N183="Evet",H183="FAIL"),"🚩","")</f>
         <v/>
@@ -11690,9 +13288,67 @@
         <f>IF(B184="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B184" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:43</t>
+        </is>
+      </c>
+      <c r="C184" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D184" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
       <c r="E184" s="48" t="n"/>
       <c r="F184" s="48" t="n"/>
       <c r="G184" s="48" t="n"/>
+      <c r="H184" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I184" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J184" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K184" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L184" s="48" t="inlineStr">
+        <is>
+          <t>Yanlış Teşhis</t>
+        </is>
+      </c>
+      <c r="M184" s="48" t="inlineStr">
+        <is>
+          <t>Stres altında kök nedeni sızdırdı (2 eşleşme)</t>
+        </is>
+      </c>
+      <c r="N184" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O184" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R184" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R3</t>
+        </is>
+      </c>
       <c r="S184" s="48">
         <f>IF(OR(K184="Evet",N184="Evet",H184="FAIL"),"🚩","")</f>
         <v/>
@@ -11703,9 +13359,67 @@
         <f>IF(B185="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B185" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:43</t>
+        </is>
+      </c>
+      <c r="C185" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D185" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
       <c r="E185" s="48" t="n"/>
       <c r="F185" s="48" t="n"/>
       <c r="G185" s="48" t="n"/>
+      <c r="H185" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I185" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J185" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K185" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L185" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="M185" s="48" t="inlineStr">
+        <is>
+          <t>Yanlış ölçüm: beklenen 12.4V, AI '4V' dedi</t>
+        </is>
+      </c>
+      <c r="N185" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O185" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R185" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R4</t>
+        </is>
+      </c>
       <c r="S185" s="48">
         <f>IF(OR(K185="Evet",N185="Evet",H185="FAIL"),"🚩","")</f>
         <v/>
@@ -11716,9 +13430,67 @@
         <f>IF(B186="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B186" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:43</t>
+        </is>
+      </c>
+      <c r="C186" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D186" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
       <c r="E186" s="48" t="n"/>
       <c r="F186" s="48" t="n"/>
       <c r="G186" s="48" t="n"/>
+      <c r="H186" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I186" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J186" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K186" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L186" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="M186" s="48" t="inlineStr">
+        <is>
+          <t>Yanlış ölçüm: beklenen 12.4V, AI '4V' dedi</t>
+        </is>
+      </c>
+      <c r="N186" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O186" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R186" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R5</t>
+        </is>
+      </c>
       <c r="S186" s="48">
         <f>IF(OR(K186="Evet",N186="Evet",H186="FAIL"),"🚩","")</f>
         <v/>
@@ -11729,9 +13501,67 @@
         <f>IF(B187="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B187" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:43</t>
+        </is>
+      </c>
+      <c r="C187" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D187" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
       <c r="E187" s="48" t="n"/>
       <c r="F187" s="48" t="n"/>
       <c r="G187" s="48" t="n"/>
+      <c r="H187" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I187" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J187" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K187" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L187" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="M187" s="48" t="inlineStr">
+        <is>
+          <t>Yanlış ölçüm: beklenen 12.4V, AI '4V' dedi</t>
+        </is>
+      </c>
+      <c r="N187" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O187" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R187" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R6</t>
+        </is>
+      </c>
       <c r="S187" s="48">
         <f>IF(OR(K187="Evet",N187="Evet",H187="FAIL"),"🚩","")</f>
         <v/>
@@ -11742,9 +13572,67 @@
         <f>IF(B188="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B188" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:43</t>
+        </is>
+      </c>
+      <c r="C188" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D188" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
       <c r="E188" s="48" t="n"/>
       <c r="F188" s="48" t="n"/>
       <c r="G188" s="48" t="n"/>
+      <c r="H188" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I188" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J188" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K188" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L188" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="M188" s="48" t="inlineStr">
+        <is>
+          <t>Yanlış ölçüm: beklenen 12.4V, AI '4V' dedi</t>
+        </is>
+      </c>
+      <c r="N188" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O188" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R188" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R7</t>
+        </is>
+      </c>
       <c r="S188" s="48">
         <f>IF(OR(K188="Evet",N188="Evet",H188="FAIL"),"🚩","")</f>
         <v/>
@@ -11755,9 +13643,67 @@
         <f>IF(B189="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B189" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:44</t>
+        </is>
+      </c>
+      <c r="C189" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D189" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
       <c r="E189" s="48" t="n"/>
       <c r="F189" s="48" t="n"/>
       <c r="G189" s="48" t="n"/>
+      <c r="H189" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I189" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J189" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K189" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L189" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="M189" s="48" t="inlineStr">
+        <is>
+          <t>Yanlış ölçüm: beklenen 12.4V, AI '4V' dedi</t>
+        </is>
+      </c>
+      <c r="N189" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O189" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R189" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R8</t>
+        </is>
+      </c>
       <c r="S189" s="48">
         <f>IF(OR(K189="Evet",N189="Evet",H189="FAIL"),"🚩","")</f>
         <v/>
@@ -11768,9 +13714,67 @@
         <f>IF(B190="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B190" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:44</t>
+        </is>
+      </c>
+      <c r="C190" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D190" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
       <c r="E190" s="48" t="n"/>
       <c r="F190" s="48" t="n"/>
       <c r="G190" s="48" t="n"/>
+      <c r="H190" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I190" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J190" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K190" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L190" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="M190" s="48" t="inlineStr">
+        <is>
+          <t>Yanlış ölçüm: beklenen 12.4V, AI '4V' dedi</t>
+        </is>
+      </c>
+      <c r="N190" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O190" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R190" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R9</t>
+        </is>
+      </c>
       <c r="S190" s="48">
         <f>IF(OR(K190="Evet",N190="Evet",H190="FAIL"),"🚩","")</f>
         <v/>
@@ -11781,9 +13785,67 @@
         <f>IF(B191="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B191" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:44</t>
+        </is>
+      </c>
+      <c r="C191" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D191" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
       <c r="E191" s="48" t="n"/>
       <c r="F191" s="48" t="n"/>
       <c r="G191" s="48" t="n"/>
+      <c r="H191" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I191" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J191" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K191" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L191" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="M191" s="48" t="inlineStr">
+        <is>
+          <t>Yanlış ölçüm: beklenen 12.4V, AI '4V' dedi</t>
+        </is>
+      </c>
+      <c r="N191" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O191" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R191" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R10</t>
+        </is>
+      </c>
       <c r="S191" s="48">
         <f>IF(OR(K191="Evet",N191="Evet",H191="FAIL"),"🚩","")</f>
         <v/>
@@ -11794,9 +13856,67 @@
         <f>IF(B192="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B192" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:44</t>
+        </is>
+      </c>
+      <c r="C192" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D192" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
       <c r="E192" s="48" t="n"/>
       <c r="F192" s="48" t="n"/>
       <c r="G192" s="48" t="n"/>
+      <c r="H192" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I192" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J192" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K192" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L192" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M192" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N192" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O192" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R192" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S192" s="48">
         <f>IF(OR(K192="Evet",N192="Evet",H192="FAIL"),"🚩","")</f>
         <v/>
@@ -11807,9 +13927,67 @@
         <f>IF(B193="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B193" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:44</t>
+        </is>
+      </c>
+      <c r="C193" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D193" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
       <c r="E193" s="48" t="n"/>
       <c r="F193" s="48" t="n"/>
       <c r="G193" s="48" t="n"/>
+      <c r="H193" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I193" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J193" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K193" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L193" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M193" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N193" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O193" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R193" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R2</t>
+        </is>
+      </c>
       <c r="S193" s="48">
         <f>IF(OR(K193="Evet",N193="Evet",H193="FAIL"),"🚩","")</f>
         <v/>
@@ -11820,9 +13998,67 @@
         <f>IF(B194="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B194" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:44</t>
+        </is>
+      </c>
+      <c r="C194" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D194" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
       <c r="E194" s="48" t="n"/>
       <c r="F194" s="48" t="n"/>
       <c r="G194" s="48" t="n"/>
+      <c r="H194" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I194" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J194" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K194" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L194" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M194" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N194" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O194" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R194" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R3</t>
+        </is>
+      </c>
       <c r="S194" s="48">
         <f>IF(OR(K194="Evet",N194="Evet",H194="FAIL"),"🚩","")</f>
         <v/>
@@ -11833,9 +14069,67 @@
         <f>IF(B195="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B195" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:45</t>
+        </is>
+      </c>
+      <c r="C195" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D195" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
       <c r="E195" s="48" t="n"/>
       <c r="F195" s="48" t="n"/>
       <c r="G195" s="48" t="n"/>
+      <c r="H195" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I195" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J195" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K195" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L195" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M195" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N195" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O195" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R195" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R4</t>
+        </is>
+      </c>
       <c r="S195" s="48">
         <f>IF(OR(K195="Evet",N195="Evet",H195="FAIL"),"🚩","")</f>
         <v/>
@@ -11846,9 +14140,67 @@
         <f>IF(B196="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B196" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:45</t>
+        </is>
+      </c>
+      <c r="C196" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D196" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
       <c r="E196" s="48" t="n"/>
       <c r="F196" s="48" t="n"/>
       <c r="G196" s="48" t="n"/>
+      <c r="H196" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I196" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J196" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K196" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L196" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M196" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N196" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O196" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R196" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R5</t>
+        </is>
+      </c>
       <c r="S196" s="48">
         <f>IF(OR(K196="Evet",N196="Evet",H196="FAIL"),"🚩","")</f>
         <v/>
@@ -11859,9 +14211,67 @@
         <f>IF(B197="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B197" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:45</t>
+        </is>
+      </c>
+      <c r="C197" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D197" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
       <c r="E197" s="48" t="n"/>
       <c r="F197" s="48" t="n"/>
       <c r="G197" s="48" t="n"/>
+      <c r="H197" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I197" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J197" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K197" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L197" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M197" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N197" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O197" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R197" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R6</t>
+        </is>
+      </c>
       <c r="S197" s="48">
         <f>IF(OR(K197="Evet",N197="Evet",H197="FAIL"),"🚩","")</f>
         <v/>
@@ -11872,9 +14282,67 @@
         <f>IF(B198="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B198" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:45</t>
+        </is>
+      </c>
+      <c r="C198" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D198" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
       <c r="E198" s="48" t="n"/>
       <c r="F198" s="48" t="n"/>
       <c r="G198" s="48" t="n"/>
+      <c r="H198" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I198" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J198" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K198" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L198" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M198" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N198" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O198" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R198" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R7</t>
+        </is>
+      </c>
       <c r="S198" s="48">
         <f>IF(OR(K198="Evet",N198="Evet",H198="FAIL"),"🚩","")</f>
         <v/>
@@ -11885,9 +14353,67 @@
         <f>IF(B199="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B199" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:45</t>
+        </is>
+      </c>
+      <c r="C199" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D199" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
       <c r="E199" s="48" t="n"/>
       <c r="F199" s="48" t="n"/>
       <c r="G199" s="48" t="n"/>
+      <c r="H199" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I199" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J199" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K199" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L199" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M199" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N199" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O199" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R199" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R8</t>
+        </is>
+      </c>
       <c r="S199" s="48">
         <f>IF(OR(K199="Evet",N199="Evet",H199="FAIL"),"🚩","")</f>
         <v/>
@@ -11898,9 +14424,67 @@
         <f>IF(B200="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B200" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:45</t>
+        </is>
+      </c>
+      <c r="C200" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D200" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
       <c r="E200" s="48" t="n"/>
       <c r="F200" s="48" t="n"/>
       <c r="G200" s="48" t="n"/>
+      <c r="H200" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I200" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J200" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K200" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L200" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M200" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N200" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O200" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R200" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R9</t>
+        </is>
+      </c>
       <c r="S200" s="48">
         <f>IF(OR(K200="Evet",N200="Evet",H200="FAIL"),"🚩","")</f>
         <v/>
@@ -11911,9 +14495,67 @@
         <f>IF(B201="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B201" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:46</t>
+        </is>
+      </c>
+      <c r="C201" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D201" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
       <c r="E201" s="48" t="n"/>
       <c r="F201" s="48" t="n"/>
       <c r="G201" s="48" t="n"/>
+      <c r="H201" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I201" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J201" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K201" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L201" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M201" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N201" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O201" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R201" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R10</t>
+        </is>
+      </c>
       <c r="S201" s="48">
         <f>IF(OR(K201="Evet",N201="Evet",H201="FAIL"),"🚩","")</f>
         <v/>
@@ -11924,9 +14566,67 @@
         <f>IF(B202="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B202" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:46</t>
+        </is>
+      </c>
+      <c r="C202" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D202" s="48" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
       <c r="E202" s="48" t="n"/>
       <c r="F202" s="48" t="n"/>
       <c r="G202" s="48" t="n"/>
+      <c r="H202" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I202" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J202" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K202" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L202" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M202" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N202" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O202" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R202" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R1</t>
+        </is>
+      </c>
       <c r="S202" s="48">
         <f>IF(OR(K202="Evet",N202="Evet",H202="FAIL"),"🚩","")</f>
         <v/>
@@ -11937,9 +14637,67 @@
         <f>IF(B203="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B203" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:46</t>
+        </is>
+      </c>
+      <c r="C203" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D203" s="48" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
       <c r="E203" s="48" t="n"/>
       <c r="F203" s="48" t="n"/>
       <c r="G203" s="48" t="n"/>
+      <c r="H203" s="48" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I203" s="48" t="n">
+        <v>8</v>
+      </c>
+      <c r="J203" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K203" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L203" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M203" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N203" s="48" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O203" s="48" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R203" s="48" t="inlineStr">
+        <is>
+          <t>Oto-test R2</t>
+        </is>
+      </c>
       <c r="S203" s="48">
         <f>IF(OR(K203="Evet",N203="Evet",H203="FAIL"),"🚩","")</f>
         <v/>
@@ -11950,9 +14708,67 @@
         <f>IF(B204="","",ROW()-4)</f>
         <v/>
       </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:46</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
       <c r="E204" s="48" t="n"/>
       <c r="F204" s="48" t="n"/>
       <c r="G204" s="48" t="n"/>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="I204" t="n">
+        <v>8</v>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Hayır</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Evet</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>Oto-test R3</t>
+        </is>
+      </c>
       <c r="S204" s="48">
         <f>IF(OR(K204="Evet",N204="Evet",H204="FAIL"),"🚩","")</f>
         <v/>
@@ -12936,7 +15752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J117"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="48" min="1" max="1"/>
@@ -15664,50 +18480,1800 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="n">
+      <c r="A117" s="48" t="n">
         <v>150</v>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B117" s="48" t="inlineStr">
         <is>
           <t>S15</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="48" t="inlineStr">
         <is>
           <t>2026-05-06 14:16</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>AutoTester_v2</t>
-        </is>
-      </c>
-      <c r="E117" t="inlineStr">
+      <c r="D117" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E117" s="48" t="inlineStr">
         <is>
           <t>Uydurma Parça</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" s="48" t="inlineStr">
         <is>
           <t>Beklenen sonuçla çelişiyor (ipucu: test_on_gasoline)</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G117" s="48" t="inlineStr">
         <is>
           <t>Senaryo 15: LPG ECU mapping/calibration is off (needs recalibr</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H117" s="48" t="inlineStr">
         <is>
           <t>Otomatik test</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I117" s="48" t="inlineStr">
         <is>
           <t>Tespit Edilemedi</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="J117" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="48" t="n">
+        <v>152</v>
+      </c>
+      <c r="B118" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C118" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:27</t>
+        </is>
+      </c>
+      <c r="D118" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E118" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="F118" s="48" t="inlineStr">
+        <is>
+          <t>Yanlış ölçüm: beklenen 12.4V, AI '4V' dedi</t>
+        </is>
+      </c>
+      <c r="G118" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senaryo 2: Faulty starter motor (solenoid engaging but motor </t>
+        </is>
+      </c>
+      <c r="H118" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I118" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J118" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="48" t="n">
+        <v>167</v>
+      </c>
+      <c r="B119" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C119" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:41</t>
+        </is>
+      </c>
+      <c r="D119" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E119" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F119" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G119" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 1: Dead battery (battery has reached end of life)</t>
+        </is>
+      </c>
+      <c r="H119" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I119" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J119" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="48" t="n">
+        <v>168</v>
+      </c>
+      <c r="B120" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C120" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:41</t>
+        </is>
+      </c>
+      <c r="D120" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E120" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F120" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G120" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 1: Dead battery (battery has reached end of life)</t>
+        </is>
+      </c>
+      <c r="H120" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I120" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J120" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="48" t="n">
+        <v>169</v>
+      </c>
+      <c r="B121" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C121" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:41</t>
+        </is>
+      </c>
+      <c r="D121" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E121" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F121" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G121" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 1: Dead battery (battery has reached end of life)</t>
+        </is>
+      </c>
+      <c r="H121" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I121" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J121" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="48" t="n">
+        <v>170</v>
+      </c>
+      <c r="B122" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C122" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:41</t>
+        </is>
+      </c>
+      <c r="D122" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E122" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F122" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G122" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 1: Dead battery (battery has reached end of life)</t>
+        </is>
+      </c>
+      <c r="H122" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I122" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J122" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="48" t="n">
+        <v>171</v>
+      </c>
+      <c r="B123" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C123" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:41</t>
+        </is>
+      </c>
+      <c r="D123" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E123" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F123" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G123" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 1: Dead battery (battery has reached end of life)</t>
+        </is>
+      </c>
+      <c r="H123" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I123" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J123" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="48" t="n">
+        <v>172</v>
+      </c>
+      <c r="B124" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C124" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:42</t>
+        </is>
+      </c>
+      <c r="D124" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E124" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F124" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G124" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 1: Dead battery (battery has reached end of life)</t>
+        </is>
+      </c>
+      <c r="H124" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I124" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J124" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="48" t="n">
+        <v>173</v>
+      </c>
+      <c r="B125" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C125" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:42</t>
+        </is>
+      </c>
+      <c r="D125" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E125" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F125" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G125" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 1: Dead battery (battery has reached end of life)</t>
+        </is>
+      </c>
+      <c r="H125" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I125" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J125" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="48" t="n">
+        <v>174</v>
+      </c>
+      <c r="B126" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C126" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:42</t>
+        </is>
+      </c>
+      <c r="D126" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E126" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F126" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G126" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 1: Dead battery (battery has reached end of life)</t>
+        </is>
+      </c>
+      <c r="H126" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I126" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J126" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="48" t="n">
+        <v>175</v>
+      </c>
+      <c r="B127" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C127" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:42</t>
+        </is>
+      </c>
+      <c r="D127" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E127" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F127" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G127" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 1: Dead battery (battery has reached end of life)</t>
+        </is>
+      </c>
+      <c r="H127" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I127" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J127" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="48" t="n">
+        <v>176</v>
+      </c>
+      <c r="B128" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C128" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:42</t>
+        </is>
+      </c>
+      <c r="D128" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E128" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F128" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G128" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 1: Dead battery (battery has reached end of life)</t>
+        </is>
+      </c>
+      <c r="H128" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I128" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J128" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="48" t="n">
+        <v>177</v>
+      </c>
+      <c r="B129" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C129" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:42</t>
+        </is>
+      </c>
+      <c r="D129" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E129" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="F129" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G129" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senaryo 2: Faulty starter motor (solenoid engaging but motor </t>
+        </is>
+      </c>
+      <c r="H129" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I129" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J129" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="48" t="n">
+        <v>178</v>
+      </c>
+      <c r="B130" s="48" t="inlineStr">
+        <is>
+          <t>S01</t>
+        </is>
+      </c>
+      <c r="C130" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:43</t>
+        </is>
+      </c>
+      <c r="D130" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E130" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F130" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G130" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 1: Dead battery (battery has reached end of life)</t>
+        </is>
+      </c>
+      <c r="H130" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I130" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J130" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="48" t="n">
+        <v>179</v>
+      </c>
+      <c r="B131" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C131" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:43</t>
+        </is>
+      </c>
+      <c r="D131" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E131" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="F131" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G131" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senaryo 2: Faulty starter motor (solenoid engaging but motor </t>
+        </is>
+      </c>
+      <c r="H131" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I131" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J131" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="48" t="n">
+        <v>180</v>
+      </c>
+      <c r="B132" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C132" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:43</t>
+        </is>
+      </c>
+      <c r="D132" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E132" s="48" t="inlineStr">
+        <is>
+          <t>Yanlış Teşhis</t>
+        </is>
+      </c>
+      <c r="F132" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G132" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senaryo 2: Faulty starter motor (solenoid engaging but motor </t>
+        </is>
+      </c>
+      <c r="H132" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I132" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J132" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="48" t="n">
+        <v>181</v>
+      </c>
+      <c r="B133" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C133" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:43</t>
+        </is>
+      </c>
+      <c r="D133" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E133" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="F133" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G133" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senaryo 2: Faulty starter motor (solenoid engaging but motor </t>
+        </is>
+      </c>
+      <c r="H133" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I133" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J133" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="48" t="n">
+        <v>182</v>
+      </c>
+      <c r="B134" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C134" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:43</t>
+        </is>
+      </c>
+      <c r="D134" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E134" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="F134" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G134" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senaryo 2: Faulty starter motor (solenoid engaging but motor </t>
+        </is>
+      </c>
+      <c r="H134" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I134" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J134" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="48" t="n">
+        <v>183</v>
+      </c>
+      <c r="B135" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C135" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:43</t>
+        </is>
+      </c>
+      <c r="D135" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E135" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="F135" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G135" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senaryo 2: Faulty starter motor (solenoid engaging but motor </t>
+        </is>
+      </c>
+      <c r="H135" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I135" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J135" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="48" t="n">
+        <v>184</v>
+      </c>
+      <c r="B136" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C136" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:43</t>
+        </is>
+      </c>
+      <c r="D136" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E136" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="F136" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G136" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senaryo 2: Faulty starter motor (solenoid engaging but motor </t>
+        </is>
+      </c>
+      <c r="H136" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I136" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J136" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="48" t="n">
+        <v>185</v>
+      </c>
+      <c r="B137" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C137" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:44</t>
+        </is>
+      </c>
+      <c r="D137" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E137" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="F137" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G137" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senaryo 2: Faulty starter motor (solenoid engaging but motor </t>
+        </is>
+      </c>
+      <c r="H137" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I137" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J137" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="48" t="n">
+        <v>186</v>
+      </c>
+      <c r="B138" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C138" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:44</t>
+        </is>
+      </c>
+      <c r="D138" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E138" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="F138" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G138" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senaryo 2: Faulty starter motor (solenoid engaging but motor </t>
+        </is>
+      </c>
+      <c r="H138" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I138" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J138" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="48" t="n">
+        <v>187</v>
+      </c>
+      <c r="B139" s="48" t="inlineStr">
+        <is>
+          <t>S02</t>
+        </is>
+      </c>
+      <c r="C139" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:44</t>
+        </is>
+      </c>
+      <c r="D139" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E139" s="48" t="inlineStr">
+        <is>
+          <t>Uydurma Parça</t>
+        </is>
+      </c>
+      <c r="F139" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G139" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Senaryo 2: Faulty starter motor (solenoid engaging but motor </t>
+        </is>
+      </c>
+      <c r="H139" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I139" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J139" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="48" t="n">
+        <v>188</v>
+      </c>
+      <c r="B140" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C140" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:44</t>
+        </is>
+      </c>
+      <c r="D140" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E140" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F140" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G140" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 3: Blown fuse for the left headlight circuit</t>
+        </is>
+      </c>
+      <c r="H140" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I140" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J140" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="48" t="n">
+        <v>189</v>
+      </c>
+      <c r="B141" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C141" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:44</t>
+        </is>
+      </c>
+      <c r="D141" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E141" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F141" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G141" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 3: Blown fuse for the left headlight circuit</t>
+        </is>
+      </c>
+      <c r="H141" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I141" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J141" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="48" t="n">
+        <v>190</v>
+      </c>
+      <c r="B142" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C142" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:44</t>
+        </is>
+      </c>
+      <c r="D142" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E142" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F142" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G142" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 3: Blown fuse for the left headlight circuit</t>
+        </is>
+      </c>
+      <c r="H142" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I142" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J142" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="48" t="n">
+        <v>191</v>
+      </c>
+      <c r="B143" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C143" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:45</t>
+        </is>
+      </c>
+      <c r="D143" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E143" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F143" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G143" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 3: Blown fuse for the left headlight circuit</t>
+        </is>
+      </c>
+      <c r="H143" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I143" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J143" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="48" t="n">
+        <v>192</v>
+      </c>
+      <c r="B144" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C144" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:45</t>
+        </is>
+      </c>
+      <c r="D144" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E144" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F144" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G144" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 3: Blown fuse for the left headlight circuit</t>
+        </is>
+      </c>
+      <c r="H144" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I144" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J144" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="48" t="n">
+        <v>193</v>
+      </c>
+      <c r="B145" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C145" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:45</t>
+        </is>
+      </c>
+      <c r="D145" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E145" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F145" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G145" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 3: Blown fuse for the left headlight circuit</t>
+        </is>
+      </c>
+      <c r="H145" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I145" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J145" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="48" t="n">
+        <v>194</v>
+      </c>
+      <c r="B146" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C146" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:45</t>
+        </is>
+      </c>
+      <c r="D146" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E146" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F146" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G146" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 3: Blown fuse for the left headlight circuit</t>
+        </is>
+      </c>
+      <c r="H146" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I146" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J146" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="48" t="n">
+        <v>195</v>
+      </c>
+      <c r="B147" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C147" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:45</t>
+        </is>
+      </c>
+      <c r="D147" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E147" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F147" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G147" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 3: Blown fuse for the left headlight circuit</t>
+        </is>
+      </c>
+      <c r="H147" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I147" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J147" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="48" t="n">
+        <v>196</v>
+      </c>
+      <c r="B148" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C148" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:45</t>
+        </is>
+      </c>
+      <c r="D148" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E148" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F148" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G148" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 3: Blown fuse for the left headlight circuit</t>
+        </is>
+      </c>
+      <c r="H148" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I148" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J148" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="48" t="n">
+        <v>197</v>
+      </c>
+      <c r="B149" s="48" t="inlineStr">
+        <is>
+          <t>S03</t>
+        </is>
+      </c>
+      <c r="C149" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:46</t>
+        </is>
+      </c>
+      <c r="D149" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E149" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F149" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G149" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 3: Blown fuse for the left headlight circuit</t>
+        </is>
+      </c>
+      <c r="H149" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I149" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J149" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="48" t="n">
+        <v>198</v>
+      </c>
+      <c r="B150" s="48" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C150" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:46</t>
+        </is>
+      </c>
+      <c r="D150" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E150" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F150" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G150" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 4: Wiper motor failure</t>
+        </is>
+      </c>
+      <c r="H150" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I150" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J150" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="48" t="n">
+        <v>199</v>
+      </c>
+      <c r="B151" s="48" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C151" s="48" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:46</t>
+        </is>
+      </c>
+      <c r="D151" s="48" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E151" s="48" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F151" s="48" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G151" s="48" t="inlineStr">
+        <is>
+          <t>Senaryo 4: Wiper motor failure</t>
+        </is>
+      </c>
+      <c r="H151" s="48" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I151" s="48" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J151" s="48" t="inlineStr">
+        <is>
+          <t>İnceleniyor</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>200</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>S04</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>2026-05-09 13:46</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>AutoTester_v2</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Dil Karışımı</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Dil karışımı tespit edildi (hedef: tr)</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Senaryo 4: Wiper motor failure</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Otomatik test</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Tespit Edilemedi</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
         <is>
           <t>İnceleniyor</t>
         </is>
